--- a/result/ITGB1_LUAD_Tables.xlsx
+++ b/result/ITGB1_LUAD_Tables.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +479,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.789</t>
         </is>
       </c>
     </row>
@@ -508,342 +510,328 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.005</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>128</v>
-      </c>
-      <c r="C8" t="n">
-        <v>96</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>118</v>
+      </c>
+      <c r="C9" t="n">
+        <v>144</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.108</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.108</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="n">
-        <v>10</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>171</v>
+      </c>
+      <c r="C14" t="n">
+        <v>151</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.620</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>171</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>151</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.777</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" t="n">
-        <v>10</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>157</v>
+      </c>
+      <c r="C17" t="n">
+        <v>159</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.460</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="C18" t="n">
-        <v>159</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.460</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>54</v>
+      </c>
+      <c r="C22" t="n">
+        <v>110</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="C23" t="n">
-        <v>110</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="C24" t="n">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" t="n">
-        <v>5</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>70</v>
+      </c>
+      <c r="C27" t="n">
+        <v>89</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="C28" t="n">
-        <v>89</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.083</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>176</v>
-      </c>
-      <c r="C29" t="n">
         <v>157</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -856,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,27 +870,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -929,27 +922,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.138</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.099</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-0.091</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.066</t>
         </is>
       </c>
     </row>
@@ -957,7 +955,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -968,27 +966,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.090</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.337</t>
         </is>
       </c>
     </row>
@@ -1015,27 +1018,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>-0.016</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.074</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1051,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1054,34 +1062,39 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.774</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.181</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.611</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1091,12 +1104,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1106,22 +1119,27 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1129,45 +1147,50 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.090</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1177,17 +1200,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.138</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1197,17 +1220,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-0.102</t>
         </is>
       </c>
     </row>
@@ -1215,45 +1243,50 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.139</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1263,22 +1296,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.099</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1288,12 +1321,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.008</t>
         </is>
       </c>
     </row>
@@ -1301,45 +1339,50 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.940</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.904</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1349,27 +1392,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.110</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.067</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1379,7 +1422,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.050</t>
         </is>
       </c>
     </row>
@@ -1387,45 +1435,50 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.469</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1435,37 +1488,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-0.091</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>-0.040</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.122</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-0.069</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-0.055</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -1473,40 +1531,141 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.043</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-0.066</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.337</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1519,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1535,6 +1694,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1548,7 +1717,13 @@
       <c r="B2" t="n">
         <v>1.01</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>0.309</t>
         </is>
@@ -1563,7 +1738,13 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.929</t>
         </is>
@@ -1578,7 +1759,13 @@
       <c r="B4" t="n">
         <v>0.645</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.021</t>
         </is>
@@ -1593,7 +1780,13 @@
       <c r="B5" t="n">
         <v>1.246</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.268</t>
         </is>
@@ -1608,7 +1801,13 @@
       <c r="B6" t="n">
         <v>2.109</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>1.331</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.343</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>0.001</t>
         </is>
@@ -1623,7 +1822,13 @@
       <c r="B7" t="n">
         <v>2.767</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.449</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -1638,7 +1843,13 @@
       <c r="B8" t="n">
         <v>2.8</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.684</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -1655,12 +1866,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Clinical Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Hazard Ratio (HR)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.254</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.885</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.509</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ITGB1group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.851</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.224</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Variable</t>
         </is>
       </c>
@@ -1671,15 +2028,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1687,13 +2039,12 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
         <v/>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1708,7 +2059,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1718,12 +2068,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
+          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1733,12 +2082,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.0193</t>
+          <t>0.0150</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1748,12 +2096,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.8673e-01</t>
+          <t>1.7367e-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1764,7 +2111,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1773,17 +2119,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7969.4374</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2255.0097</v>
-      </c>
-      <c r="D8" t="n">
-        <v>13683.8651</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.006</t>
+        <v>8601.771000000001</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3085.132-14118.41</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.002</t>
         </is>
       </c>
     </row>
@@ -1794,794 +2139,1003 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>732.6941</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1007.4362</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2472.8244</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.408</t>
+        <v>779.175</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-916.593-2474.944</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.367</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>724.1683</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1366.8156</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2815.1523</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.496</t>
+        <v>65.032</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-17.738-147.802</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1136.7845</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1193.7718</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3467.3408</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.338</t>
+        <v>15.125</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-15.932-46.182</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.339</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>522.9116</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-3362.3326</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4408.1558</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.791</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>67.6365</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-16.7926</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152.0656</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.116</t>
-        </is>
-      </c>
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>17.1693</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-14.333</v>
-      </c>
-      <c r="D14" t="n">
-        <v>48.6717</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.284</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0193</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ITGB1expression</t>
+          <t>3.8673e-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0499</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7969.437</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2255.01-13683.865</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.0125e-02</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>732.694</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-1007.436-2472.824</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.408</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>724.168</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1366.816-2815.152</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.496</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_stage)[T.3.0]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6315.9348</v>
-      </c>
-      <c r="C22" t="n">
-        <v>703.1644</v>
-      </c>
-      <c r="D22" t="n">
-        <v>11928.7052</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.028</t>
+        <v>1136.784</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1193.772-3467.341</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.338</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_stage)[T.4.0]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>114.7337</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1606.0194</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1835.4869</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.896</t>
+        <v>522.912</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3362.333-4408.156</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.791</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.2.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2696.4585</v>
-      </c>
-      <c r="C24" t="n">
-        <v>861.2585</v>
-      </c>
-      <c r="D24" t="n">
-        <v>4531.6586</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.004</t>
+        <v>67.637</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-16.793-152.066</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.116</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C(pathologic_T)[T.3.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4189.4982</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1094.1505</v>
-      </c>
-      <c r="D25" t="n">
-        <v>7284.8459</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.008</t>
+        <v>17.169</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-14.333-48.672</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.284</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>3698.28</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-677.2277</v>
-      </c>
-      <c r="D26" t="n">
-        <v>8073.7878</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.097</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>72.6049</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-9.286099999999999</v>
-      </c>
-      <c r="D27" t="n">
-        <v>154.4959</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.082</t>
-        </is>
-      </c>
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>18.8884</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-11.9386</v>
-      </c>
-      <c r="D28" t="n">
-        <v>49.7154</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.229</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0499</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ITGB1expression</t>
+          <t>1.0125e-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0160</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>6315.935</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>703.164-11928.705</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.028</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>5.1845e-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>114.734</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-1606.019-1835.487</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.896</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2696.459</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>861.258-4531.659</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_T)[T.3.0]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8731.025299999999</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3003.4364</v>
-      </c>
-      <c r="D36" t="n">
-        <v>14458.6143</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.003</t>
+        <v>4189.498</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1094.15-7284.846</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.008</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_T)[T.4.0]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>742.176</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-1005.6774</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2490.0293</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.404</t>
+        <v>3698.28</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-677.228-8073.788</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.097</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.1.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-10.3278</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-2217.1379</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2196.4823</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.993</t>
+        <v>72.605</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-9.286-154.496</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.082</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C(pathologic_N)[T.2.0]</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>90.14749999999999</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-2378.9264</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2559.2213</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.943</t>
+        <v>18.888</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-11.939-49.715</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.229</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>-3659.233</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-14557.2573</v>
-      </c>
-      <c r="D40" t="n">
-        <v>7238.7913</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.509</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>64.5193</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-20.7496</v>
-      </c>
-      <c r="D41" t="n">
-        <v>149.7883</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.138</t>
-        </is>
-      </c>
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>14.3426</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-17.4134</v>
-      </c>
-      <c r="D42" t="n">
-        <v>46.0987</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.375</t>
-        </is>
-      </c>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0160</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
+          <t>Prob (F-statistic)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ITGB1expression</t>
+          <t>5.1845e-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0150</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>8731.025</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3003.436-14458.614</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>4.7688e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>742.176</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-1005.677-2490.029</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.404</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-10.328</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-2217.138-2196.482</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.993</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Intercept</t>
+          <t>C(pathologic_N)[T.2.0]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9359.9295</v>
-      </c>
-      <c r="C50" t="n">
-        <v>2312.5637</v>
-      </c>
-      <c r="D50" t="n">
-        <v>16407.2953</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.009</t>
+        <v>90.14700000000001</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-2378.926-2559.221</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.943</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C(gender)[T.MALE]</t>
+          <t>C(pathologic_N)[T.3.0]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>323.7812</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1861.0366</v>
-      </c>
-      <c r="D51" t="n">
-        <v>2508.599</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.771</t>
+        <v>-3659.233</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-14557.257-7238.791</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.509</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C(pathologic_M)[T.1.0]</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-645.0881000000001</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-4795.2164</v>
-      </c>
-      <c r="D52" t="n">
-        <v>3505.0402</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.760</t>
+        <v>64.51900000000001</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-20.75-149.788</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.138</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>number_pack_years_smoked</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>62.3646</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-43.8007</v>
-      </c>
-      <c r="D53" t="n">
-        <v>168.5299</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.248</t>
+        <v>14.343</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-17.413-46.099</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.375</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>24.2972</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-15.9186</v>
-      </c>
-      <c r="D54" t="n">
-        <v>64.51300000000001</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.235</t>
-        </is>
-      </c>
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ITGB1expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0150</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>4.7688e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>9359.93</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2312.564-16407.295</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.009</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>323.781</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-1861.037-2508.599</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.771</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-645.088</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-4795.216-3505.04</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.760</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>62.365</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-43.801-168.53</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>24.297</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-15.919-64.513</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.235</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ITGB1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.458</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ITGB1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9.860</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
